--- a/LoanOfficer-A/2023/49 Salam Sunanda wed.xlsx
+++ b/LoanOfficer-A/2023/49 Salam Sunanda wed.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>24000</v>
+        <v>18200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -863,9 +863,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>45504</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1600</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -889,9 +895,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45515</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -915,9 +927,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45536</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -941,9 +959,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45551</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
